--- a/AAII_Financials/Yearly/ICU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ICU_YR_FIN.xlsx
@@ -939,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1031,7 +1031,7 @@
         <v>18000</v>
       </c>
       <c r="F17" s="3">
-        <v>14200</v>
+        <v>14000</v>
       </c>
       <c r="G17" s="3">
         <v>11600</v>
@@ -1070,7 +1070,7 @@
         <v>-17800</v>
       </c>
       <c r="F18" s="3">
-        <v>-14200</v>
+        <v>-14000</v>
       </c>
       <c r="G18" s="3">
         <v>-11600</v>
@@ -1165,7 +1165,7 @@
         <v>-24700</v>
       </c>
       <c r="F21" s="3">
-        <v>-20200</v>
+        <v>-20000</v>
       </c>
       <c r="G21" s="3">
         <v>-11600</v>
